--- a/Codelist Excel Files and Conversion Templates to XML/correctiveAction.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/correctiveAction.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes for action taken to address the CAUSE of a non-conformance so that it does not recur, used for the value of the correctiveAction property of diggs:NonConformance. Deliberately distinct from disposition on the same object, which concerns what happens to the affected work itself; recording only one of the two is common, but conflating them loses a distinction a reviewer needs. Repeatable, since one finding commonly triggers more than one change. Not to be confused with diggs:RIConstructionActivity/groutLevelCorrectiveAction, which is a narrow, in-progress, rigid-inclusion-specific response to one failure mode rather than a systemic change. Built at W3 - see docs/build/W3/NOTES.md. PROVISIONAL pending SME review.</t>
+          <t>Codes for action taken to address the CAUSE of a non-conformance so that it does not recur, used for the value of the correctiveAction property of diggs:NonConformance. Deliberately distinct from disposition on the same object, which concerns what happens to the affected work itself; recording only one of the two is common, but conflating them loses a distinction a reviewer needs. Repeatable, since one finding commonly triggers more than one change. Not to be confused with diggs:RIColumnConstruction/groutLevelCorrectiveAction, which is a narrow, in-progress, rigid-inclusion-specific response to one failure mode rather than a systemic change. Built at W3 - see docs/build/W3/NOTES.md. PROVISIONAL pending SME review.</t>
         </is>
       </c>
     </row>
